--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -1230,10 +1230,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://leicesterleicestershireandrutland.icb.nhs.uk/about/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>https://leicesterleicestershireandrutland.icb.nhs.uk/contact/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>foi_source_url updated 2026-09-12: /about/freedom-of-information/ now 404s and no replacement FOI page exists; llricb-llr.FOI@nhs.net is published on the /contact/ page, which is now cited instead. Address unchanged.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1633,7 +1637,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.selondonics.org/contact-us/</t>
+          <t>https://www.selondonics.org/who-we-are/contact-us/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1644,10 +1648,14 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.selondonics.org/contact-us/</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>https://www.selondonics.org/who-we-are/contact-us/</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>source_urls updated 2026-09-12: /contact-us/ now 301-redirects to /who-we-are/contact-us/. Page emails are Cloudflare-obfuscated; decoded this run to media@selondonics.nhs.uk and FOI@selondonics.nhs.uk, both matching the stored values (addresses unchanged).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -1923,10 +1923,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>wnlicb.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>nhsnwl.foi@nhs.net</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>https://www.westandnorthlondon.icb.nhs.uk/how-we-are-run/your-information-feedback-and-your-rights/freedom-information-requests</t>
@@ -1934,7 +1938,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>New merged entity from 1 April 2026 (NCL + NW London). Site is hosted at nwlondonicb.nhs.uk with new branding at westandnorthlondon.icb.nhs.uk.</t>
+          <t>New merged entity from 1 April 2026 (NCL + NW London). Site is hosted at nwlondonicb.nhs.uk with new branding at westandnorthlondon.icb.nhs.uk. foi_email primary updated 2026-09-19 from https://www.westandnorthlondon.icb.nhs.uk/how-we-are-run/your-information-feedback-and-your-rights/freedom-information-requests; prior value nhsnwl.foi@nhs.net moved to foi_email_alt.</t>
         </is>
       </c>
     </row>

--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -895,7 +895,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://ourdorset.org.uk/media/</t>
+          <t>https://staywelldorset.nhs.uk/media/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -909,7 +909,11 @@
           <t>https://nhsdorset.nhs.uk/about/foi/</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-10-10: press_source_url updated to https://staywelldorset.nhs.uk/media/ (ourdorset.org.uk/media/ now 301s there); communication@nhsdorset.nhs.uk unchanged. FOI.Requests@nhsdorset.nhs.uk confirmed on /about/foi/.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1357,14 +1361,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>nsicb.accesstoinformation@nhs.net</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>nsicb.foi@nhs.net</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>nwicb.foi@nhs.net</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>https://www.norfolkandsuffolk.icb.nhs.uk/about/governance/foi/</t>
@@ -1372,7 +1376,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Email obfuscated via Cloudflare; decoded from data-cfemail (legacy Norfolk and Waveney prefix) primary updated 2026-07-30 from https://www.norfolkandsuffolk.icb.nhs.uk/contact/ and https://www.norfolkandsuffolk.icb.nhs.uk/about/governance/foi/ (cfemail-decoded); prior nwicb.* values moved to _alt.</t>
+          <t>Email obfuscated via Cloudflare; decoded from data-cfemail (legacy Norfolk and Waveney prefix) primary updated 2026-07-30 from https://www.norfolkandsuffolk.icb.nhs.uk/contact/ and https://www.norfolkandsuffolk.icb.nhs.uk/about/governance/foi/ (cfemail-decoded); prior nwicb.* values moved to _alt. | foi primary updated 2026-10-10 from https://www.norfolkandsuffolk.icb.nhs.uk/about/governance/foi/ (cfemail-decoded; the FOI page now gives nsicb.accesstoinformation@nhs.net as the sole FOI contact); prior value nsicb.foi@nhs.net moved to _alt, displacing legacy nwicb.foi@nhs.net. Press nsicb.communications@nhs.net re-confirmed same date.</t>
         </is>
       </c>
     </row>

--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -658,14 +658,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>ceicb.contactus@nhs.net</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>blmkicb.contactus@nhs.net</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>foi@centraleast.nhs.uk</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>https://www.centraleast.icb.nhs.uk/about/requests/foi/</t>
@@ -673,7 +673,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>New merged entity from 1 April 2026 (BLMK + Cambs &amp; Peterborough + Herts &amp; West Essex). Use BLMK predecessor address for now per Dave May 2026 â€” new ICB site offers only a contact form. [2026-08-01] foi_email primary updated 2026-08-01 from https://www.centraleast.icb.nhs.uk/about/requests/foi/ — the FOI-team address on that page is Cloudflare-obfuscated and decodes to blmkicb.contactus@nhs.net; the previous primary foi@centraleast.nhs.uk no longer appears anywhere on the page and moved to _alt.</t>
+          <t>New merged entity from 1 April 2026 (BLMK + Cambs &amp; Peterborough + Herts &amp; West Essex). Use BLMK predecessor address for now per Dave May 2026 â€” new ICB site offers only a contact form. [2026-08-01] foi_email primary updated 2026-08-01 from https://www.centraleast.icb.nhs.uk/about/requests/foi/ — the FOI-team address on that page is Cloudflare-obfuscated and decodes to blmkicb.contactus@nhs.net; the previous primary foi@centraleast.nhs.uk no longer appears anywhere on the page and moved to _alt. [2026-10-17] foi_email primary updated 2026-10-17 from [https://www.centraleast.icb.nhs.uk/about/requests/foi/]; prior value moved to _alt</t>
         </is>
       </c>
     </row>
@@ -1802,18 +1802,22 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>sxicb.surreyandsussex.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>sxicb.foi@nhs.net</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.sussex.ics.nhs.uk/nhs-sussex/freedom-of-information/</t>
+          <t>https://www.surreysussex.icb.nhs.uk/freedom-of-information-requests</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Legacy Sussex ICB address â€” new Surrey and Sussex site has form only. Likely still routed correctly.; Input seed was Sussex ICS website; Surrey may have separate contact [2026-08-01] press_email primary updated 2026-08-01 from https://www.surreysussex.icb.nhs.uk/contact-us/; prior value sxicb.comms@nhs.net moved to _alt. The ICB moved to the surreysussex.icb.nhs.uk domain on 1 April 2026 and states the old sussex.ics.nhs.uk site is no longer updated and will be archived — FOI is still only published on the old site (sxicb.foi@nhs.net, unchanged), so foi_source_url is left pointing there for now and should be revisited once the new site publishes an FOI page.</t>
+          <t>Legacy Sussex ICB address â€” new Surrey and Sussex site has form only. Likely still routed correctly.; Input seed was Sussex ICS website; Surrey may have separate contact [2026-08-01] press_email primary updated 2026-08-01 from https://www.surreysussex.icb.nhs.uk/contact-us/; prior value sxicb.comms@nhs.net moved to _alt. The ICB moved to the surreysussex.icb.nhs.uk domain on 1 April 2026 and states the old sussex.ics.nhs.uk site is no longer updated and will be archived — FOI is still only published on the old site (sxicb.foi@nhs.net, unchanged), so foi_source_url is left pointing there for now and should be revisited once the new site publishes an FOI page. [2026-10-17] foi_email primary updated 2026-10-17 from [https://www.surreysussex.icb.nhs.uk/freedom-of-information-requests]; prior value moved to _alt</t>
         </is>
       </c>
     </row>

--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -426,7 +426,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
@@ -1763,16 +1763,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>stw.ssot.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>staffsstokefoi@staffsstoke.icb.nhs.uk</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://staffsstoke.icb.nhs.uk/your-nhs-integrated-care-board/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>https://www.staffsstoke.icb.nhs.uk/contact-us/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>foi primary updated 2026-10-24 from https://www.staffsstoke.icb.nhs.uk/contact-us/freedom-of-information/; prior value staffsstokefoi@staffsstoke.icb.nhs.uk moved to _alt</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1834,14 +1842,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>tvicb.media@nhs.net</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>bobicb.media@nhs.net</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>frimleyicb.public@nhs.net</t>
-        </is>
-      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>https://thamesvalley.icb.nhs.uk/contact-us</t>
@@ -1849,14 +1857,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>tvicb.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>frimleyicb.foi@nhs.net</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>SCWCSU.FOI@nhs.net</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>https://thamesvalley.icb.nhs.uk/contact-us/freedom-of-information</t>
@@ -1864,7 +1872,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Predecessor Frimley general address â€” new merged Thames Valley ICB has no dedicated press email yet.; Email obfuscated on page (joomla-hidden-mail base64); decoded from page source. Handled by South Central and West CSU | press primary updated 2026-06-06 from https://thamesvalley.icb.nhs.uk/contact-us (dedicated media address bobicb.media@nhs.net now shown; prior frimleyicb.public@nhs.net to _alt); foi primary updated 2026-06-06 from https://thamesvalley.icb.nhs.uk/contact-us/freedom-of-information (frimleyicb.foi@nhs.net now shown; prior SCWCSU.FOI@nhs.net to _alt).</t>
+          <t>Predecessor Frimley general address â€” new merged Thames Valley ICB has no dedicated press email yet.; Email obfuscated on page (joomla-hidden-mail base64); decoded from page source. Handled by South Central and West CSU | press primary updated 2026-06-06 from https://thamesvalley.icb.nhs.uk/contact-us (dedicated media address bobicb.media@nhs.net now shown; prior frimleyicb.public@nhs.net to _alt); foi primary updated 2026-06-06 from https://thamesvalley.icb.nhs.uk/contact-us/freedom-of-information (frimleyicb.foi@nhs.net now shown; prior SCWCSU.FOI@nhs.net to _alt). | press primary updated 2026-10-24 from https://thamesvalley.icb.nhs.uk/contact-us; prior value bobicb.media@nhs.net moved to _alt (displacing prior _alt frimleyicb.public@nhs.net) | foi primary updated 2026-10-24 from https://thamesvalley.icb.nhs.uk/contact-us/freedom-of-information; prior value frimleyicb.foi@nhs.net moved to _alt (displacing prior _alt SCWCSU.FOI@nhs.net)</t>
         </is>
       </c>
     </row>
